--- a/data/employees/EMP023/AST-EMP023-06.xlsx
+++ b/data/employees/EMP023/AST-EMP023-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Data Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,184 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Experiment Data Log - Taylor Miller (R&amp;D)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Director | Location: Hsinchu | Date: 2025-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Experiment ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Next Steps</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP-2026-041</t>
+          <t>EMP023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low-temp deposition</t>
+          <t>Ast Emp023 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>78</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP disclosure</t>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP-2026-042</t>
+          <t>EMP023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novel etchant blend</t>
+          <t>Ast Emp023 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Section 1: Automation backlog refinement. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP-2026-043</t>
+          <t>EMP023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surface treatment A</t>
+          <t>Ast Emp023 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.51</v>
+        <v>96</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Redesign</t>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP-2026-044</t>
+          <t>EMP023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plasma optimisation</t>
+          <t>Ast Emp023 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start Q3</t>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>95</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>94</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>99</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>89</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>67</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>67</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>96</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>87</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>69</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>94</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp023 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP023</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP023 contributes to ast emp023 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>